--- a/data/Наработка на отказ.xlsx
+++ b/data/Наработка на отказ.xlsx
@@ -440,7 +440,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>Период отчета: 01.01.2021 - 31.12.2025</t>
+          <t>Период отчета: 01.01.2025 - 31.12.2025</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13.03.2024 15:00:00</t>
+          <t>13.03.2025 15:00:00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13.03.2024 17:00:00</t>
+          <t>13.03.2025 17:00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>28.08.2023 18:00:00</t>
+          <t>28.08.2025 18:00:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>08.01.2021 16:00:00</t>
+          <t>08.01.2025 16:00:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -629,12 +629,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27.10.2022 11:00:00</t>
+          <t>27.10.2025 11:00:00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29.10.2022 13:00:00</t>
+          <t>29.10.2025 13:00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.07.2022 17:00:00</t>
+          <t>20.07.2025 17:00:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>06.11.2021 8:00:00</t>
+          <t>06.11.2025 8:00:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>14.01.2021 19:00:00</t>
+          <t>14.01.2025 19:00:00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15.01.2021 14:00:00</t>
+          <t>15.01.2025 14:00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15.03.2020 16:00:00</t>
+          <t>15.03.2025 16:00:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -764,12 +764,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13.07.2021 11:00:00</t>
+          <t>13.07.2025 11:00:00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13.07.2021 13:00:00</t>
+          <t>13.07.2025 13:00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>29.12.2020 11:00:00</t>
+          <t>29.12.2025 11:00:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22.08.2022 17:00:00</t>
+          <t>22.08.2025 17:00:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>18.08.2019 14:00:00</t>
+          <t>18.08.2025 14:00:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22.07.2024 15:00:00</t>
+          <t>22.07.2025 15:00:00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>24.07.2024 10:00:00</t>
+          <t>24.07.2025 10:00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>02.06.2022 13:00:00</t>
+          <t>02.06.2025 13:00:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>02.07.2023 12:00:00</t>
+          <t>02.07.2025 12:00:00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>04.07.2023 10:00:00</t>
+          <t>04.07.2025 10:00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30.03.2020 10:00:00</t>
+          <t>30.03.2025 10:00:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>16.03.2024 14:00:00</t>
+          <t>16.03.2025 14:00:00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>16.03.2024 19:00:00</t>
+          <t>16.03.2025 19:00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>24.06.2023 10:00:00</t>
+          <t>24.06.2025 10:00:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24.02.2024 12:00:00</t>
+          <t>24.02.2025 12:00:00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>26.02.2024 16:00:00</t>
+          <t>26.02.2025 16:00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>19.09.2021 18:00:00</t>
+          <t>19.09.2025 18:00:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19.08.2021 11:00:00</t>
+          <t>19.08.2025 11:00:00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21.08.2021 6:00:00</t>
+          <t>21.08.2025 6:00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18.01.2021 12:00:00</t>
+          <t>18.01.2025 12:00:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>30.06.2024 11:00:00</t>
+          <t>30.06.2025 11:00:00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>30.06.2024 10:00:00</t>
+          <t>30.06.2025 10:00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>03.07.2019 9:00:00</t>
+          <t>03.07.2025 9:00:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13.05.2022 7:00:00</t>
+          <t>13.05.2025 7:00:00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>13.05.2022 15:00:00</t>
+          <t>13.05.2025 15:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>29.01.2019 15:00:00</t>
+          <t>29.01.2025 15:00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>25.01.2024 16:00:00</t>
+          <t>25.01.2025 16:00:00</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>27.01.2024 6:00:00</t>
+          <t>27.01.2025 6:00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>01.06.2024 14:00:00</t>
+          <t>01.06.2025 14:00:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>31.03.2021 17:00:00</t>
+          <t>31.03.2025 17:00:00</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>01.04.2021 14:00:00</t>
+          <t>01.04.2025 14:00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>04.05.2019 8:00:00</t>
+          <t>04.05.2025 8:00:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13.04.2022 9:00:00</t>
+          <t>13.04.2025 9:00:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12.02.2022 20:00:00</t>
+          <t>12.02.2025 20:00:00</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14.02.2022 22:00:00</t>
+          <t>14.02.2025 22:00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>22.02.2022 12:00:00</t>
+          <t>22.02.2025 12:00:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>21.11.2022 16:00:00</t>
+          <t>21.11.2025 16:00:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11.02.2024 16:00:00</t>
+          <t>11.02.2025 16:00:00</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>12.02.2024 10:00:00</t>
+          <t>12.02.2025 10:00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>13.09.2020 9:00:00</t>
+          <t>13.09.2025 9:00:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>05.05.2023 20:00:00</t>
+          <t>05.05.2025 20:00:00</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>06.05.2023 16:00:00</t>
+          <t>06.05.2025 16:00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>09.11.2019 15:00:00</t>
+          <t>09.11.2025 15:00:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>29.08.2024 17:00:00</t>
+          <t>29.08.2025 17:00:00</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>29.08.2024 22:00:00</t>
+          <t>29.08.2025 22:00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>08.04.2021 10:00:00</t>
+          <t>08.04.2025 10:00:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13.10.2022 19:00:00</t>
+          <t>13.10.2025 19:00:00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>13.10.2022 10:00:00</t>
+          <t>13.10.2025 10:00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>27.12.2021 8:00:00</t>
+          <t>27.12.2025 8:00:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23.04.2023 9:00:00</t>
+          <t>23.04.2025 9:00:00</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>24.04.2023 9:00:00</t>
+          <t>24.04.2025 9:00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>08.03.2023 10:00:00</t>
+          <t>08.03.2025 10:00:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>06.05.2024 18:00:00</t>
+          <t>06.05.2025 18:00:00</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>07.05.2024 21:00:00</t>
+          <t>07.05.2025 21:00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>17.04.2019 10:00:00</t>
+          <t>17.04.2025 10:00:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>29.12.2024 8:00:00</t>
+          <t>29.12.2025 8:00:00</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>31.12.2024 12:00:00</t>
+          <t>31.12.2025 12:00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>07.05.2023 11:00:00</t>
+          <t>07.05.2025 11:00:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>28.09.2019 13:00:00</t>
+          <t>28.09.2025 13:00:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>29.11.2023 14:00:00</t>
+          <t>29.11.2025 14:00:00</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>01.12.2023 7:00:00</t>
+          <t>01.12.2025 7:00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>14.02.2023 11:00:00</t>
+          <t>14.02.2025 11:00:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>03.08.2023 20:00:00</t>
+          <t>03.08.2025 20:00:00</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>03.08.2023 10:00:00</t>
+          <t>03.08.2025 10:00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>25.08.2020 15:00:00</t>
+          <t>25.08.2025 15:00:00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>05.07.2021 11:00:00</t>
+          <t>05.07.2025 11:00:00</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>07.07.2021 20:00:00</t>
+          <t>07.07.2025 20:00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>04.01.2020 8:00:00</t>
+          <t>04.01.2025 8:00:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>04.07.2021 17:00:00</t>
+          <t>04.07.2025 17:00:00</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>05.07.2021 20:00:00</t>
+          <t>05.07.2025 20:00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>02.12.2019 18:00:00</t>
+          <t>02.12.2025 18:00:00</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>19.12.2024 12:00:00</t>
+          <t>19.12.2025 12:00:00</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21.12.2024 7:00:00</t>
+          <t>21.12.2025 7:00:00</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>26.09.2024 10:00:00</t>
+          <t>26.09.2025 10:00:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>30.07.2019 12:00:00</t>
+          <t>30.07.2025 12:00:00</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>27.09.2021 19:00:00</t>
+          <t>27.09.2025 19:00:00</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>28.09.2021 21:00:00</t>
+          <t>28.09.2025 21:00:00</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>02.06.2020 16:00:00</t>
+          <t>02.06.2025 16:00:00</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>19.07.2023 14:00:00</t>
+          <t>19.07.2025 14:00:00</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>21.07.2023 14:00:00</t>
+          <t>21.07.2025 14:00:00</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>12.06.2019 17:00:00</t>
+          <t>12.06.2025 17:00:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11.04.2021 19:00:00</t>
+          <t>11.04.2025 19:00:00</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>12.04.2021 7:00:00</t>
+          <t>12.04.2025 7:00:00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>23.04.2019 18:00:00</t>
+          <t>23.04.2025 18:00:00</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>12.08.2021 17:00:00</t>
+          <t>12.08.2025 17:00:00</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14.08.2021 11:00:00</t>
+          <t>14.08.2025 11:00:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>27.11.2019 15:00:00</t>
+          <t>27.11.2025 15:00:00</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>15.03.2021 19:00:00</t>
+          <t>15.03.2025 19:00:00</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>15.03.2021 8:00:00</t>
+          <t>15.03.2025 8:00:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>23.10.2020 14:00:00</t>
+          <t>23.10.2025 14:00:00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>06.11.2022 15:00:00</t>
+          <t>06.11.2025 15:00:00</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>08.11.2022 7:00:00</t>
+          <t>08.11.2025 7:00:00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>10.12.2021 9:00:00</t>
+          <t>10.12.2025 9:00:00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>25.05.2023 15:00:00</t>
+          <t>25.05.2025 15:00:00</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>26.05.2023 21:00:00</t>
+          <t>26.05.2025 21:00:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>12.12.2021 16:00:00</t>
+          <t>12.12.2025 16:00:00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>06.10.2023 6:00:00</t>
+          <t>06.10.2025 6:00:00</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>07.10.2023 9:00:00</t>
+          <t>07.10.2025 9:00:00</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>21.04.2020 8:00:00</t>
+          <t>21.04.2025 8:00:00</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>28.04.2023 9:00:00</t>
+          <t>28.04.2025 9:00:00</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>28.04.2023 15:00:00</t>
+          <t>28.04.2025 15:00:00</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>17.12.2020 12:00:00</t>
+          <t>17.12.2025 12:00:00</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>22.08.2021 9:00:00</t>
+          <t>22.08.2025 9:00:00</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>23.08.2021 16:00:00</t>
+          <t>23.08.2025 16:00:00</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>22.03.2021 13:00:00</t>
+          <t>22.03.2025 13:00:00</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>30.08.2023 13:00:00</t>
+          <t>30.08.2025 13:00:00</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>30.08.2023 16:00:00</t>
+          <t>30.08.2025 16:00:00</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>06.10.2019 15:00:00</t>
+          <t>06.10.2025 15:00:00</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>06.09.2022 16:00:00</t>
+          <t>06.09.2025 16:00:00</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>07.09.2022 16:00:00</t>
+          <t>07.09.2025 16:00:00</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>02.01.2022 13:00:00</t>
+          <t>02.01.2025 13:00:00</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>29.07.2022 12:00:00</t>
+          <t>29.07.2025 12:00:00</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>29.07.2022 11:00:00</t>
+          <t>29.07.2025 11:00:00</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>07.02.2021 17:00:00</t>
+          <t>07.02.2025 17:00:00</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>11.07.2022 19:00:00</t>
+          <t>11.07.2025 19:00:00</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>13.07.2022 15:00:00</t>
+          <t>13.07.2025 15:00:00</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>14.10.2021 11:00:00</t>
+          <t>14.10.2025 11:00:00</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -2899,12 +2899,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>18.08.2021 6:00:00</t>
+          <t>18.08.2025 6:00:00</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20.08.2021 21:00:00</t>
+          <t>20.08.2025 21:00:00</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>18.02.2020 16:00:00</t>
+          <t>18.02.2025 16:00:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>28.09.2022 6:00:00</t>
+          <t>28.09.2025 6:00:00</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>29.09.2022 20:00:00</t>
+          <t>29.09.2025 20:00:00</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>21.07.2019 14:00:00</t>
+          <t>21.07.2025 14:00:00</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>26.08.2021 20:00:00</t>
+          <t>26.08.2025 20:00:00</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>26.08.2021 7:00:00</t>
+          <t>26.08.2025 7:00:00</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>01.04.2019 9:00:00</t>
+          <t>01.04.2025 9:00:00</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20.10.2022 18:00:00</t>
+          <t>20.10.2025 18:00:00</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>21.10.2022 20:00:00</t>
+          <t>21.10.2025 20:00:00</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>09.08.2020 18:00:00</t>
+          <t>09.08.2025 18:00:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>19.11.2021 11:00:00</t>
+          <t>19.11.2025 11:00:00</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20.11.2021 16:00:00</t>
+          <t>20.11.2025 16:00:00</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>01.02.2019 12:00:00</t>
+          <t>01.02.2025 12:00:00</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>09.06.2024 13:00:00</t>
+          <t>09.06.2025 13:00:00</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>10.06.2024 7:00:00</t>
+          <t>10.06.2025 7:00:00</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>23.12.2023 9:00:00</t>
+          <t>23.12.2025 9:00:00</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>24.05.2023 10:00:00</t>
+          <t>24.05.2025 10:00:00</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>26.05.2023 16:00:00</t>
+          <t>26.05.2025 16:00:00</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>14.12.2022 11:00:00</t>
+          <t>14.12.2025 11:00:00</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>08.03.2024 16:00:00</t>
+          <t>08.03.2025 16:00:00</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>08.03.2024 20:00:00</t>
+          <t>08.03.2025 20:00:00</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>02.04.2024 15:00:00</t>
+          <t>02.04.2025 15:00:00</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>22.10.2021 16:00:00</t>
+          <t>22.10.2025 16:00:00</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>23.10.2021 16:00:00</t>
+          <t>23.10.2025 16:00:00</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>13.03.2021 13:00:00</t>
+          <t>13.03.2025 13:00:00</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>03.08.2023 8:00:00</t>
+          <t>03.08.2025 8:00:00</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>03.08.2023 22:00:00</t>
+          <t>03.08.2025 22:00:00</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>22.04.2023 9:00:00</t>
+          <t>22.04.2025 9:00:00</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>28.12.2023 9:00:00</t>
+          <t>28.12.2025 9:00:00</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>30.12.2023 11:00:00</t>
+          <t>30.12.2025 11:00:00</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>24.04.2022 15:00:00</t>
+          <t>24.04.2025 15:00:00</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>02.11.2022 17:00:00</t>
+          <t>02.11.2025 17:00:00</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>27.04.2024 12:00:00</t>
+          <t>27.04.2025 12:00:00</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>29.04.2024 8:00:00</t>
+          <t>29.04.2025 8:00:00</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>04.02.2020 17:00:00</t>
+          <t>04.02.2025 17:00:00</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>13.08.2024 20:00:00</t>
+          <t>13.08.2025 20:00:00</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>13.08.2024 6:00:00</t>
+          <t>13.08.2025 6:00:00</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>10.06.2021 10:00:00</t>
+          <t>10.06.2025 10:00:00</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>25.12.2023 16:00:00</t>
+          <t>25.12.2025 16:00:00</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>26.12.2023 16:00:00</t>
+          <t>26.12.2025 16:00:00</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>14.06.2022 12:00:00</t>
+          <t>14.06.2025 12:00:00</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>02.07.2021 19:00:00</t>
+          <t>02.07.2025 19:00:00</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>02.07.2021 15:00:00</t>
+          <t>02.07.2025 15:00:00</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>11.11.2021 8:00:00</t>
+          <t>11.11.2025 8:00:00</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>19.04.2021 19:00:00</t>
+          <t>19.04.2025 19:00:00</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>19.04.2021 6:00:00</t>
+          <t>19.04.2025 6:00:00</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>05.01.2021 11:00:00</t>
+          <t>05.01.2025 11:00:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>12.04.2023 13:00:00</t>
+          <t>12.04.2025 13:00:00</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>14.04.2023 10:00:00</t>
+          <t>14.04.2025 10:00:00</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>21.01.2022 11:00:00</t>
+          <t>21.01.2025 11:00:00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>27.03.2022 10:00:00</t>
+          <t>27.03.2025 10:00:00</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>23.06.2021 17:00:00</t>
+          <t>23.06.2025 17:00:00</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>23.06.2021 19:00:00</t>
+          <t>23.06.2025 19:00:00</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>01.05.2021 17:00:00</t>
+          <t>01.05.2025 17:00:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>19.05.2023 12:00:00</t>
+          <t>19.05.2025 12:00:00</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>21.05.2023 6:00:00</t>
+          <t>21.05.2025 6:00:00</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>26.02.2021 17:00:00</t>
+          <t>26.02.2025 17:00:00</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>26.03.2024 7:00:00</t>
+          <t>26.03.2025 7:00:00</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>27.03.2024 21:00:00</t>
+          <t>27.03.2025 21:00:00</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>05.06.2019 9:00:00</t>
+          <t>05.06.2025 9:00:00</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>18.10.2024 11:00:00</t>
+          <t>18.10.2025 11:00:00</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>09.06.2024 14:00:00</t>
+          <t>09.06.2025 14:00:00</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>09.06.2024 21:00:00</t>
+          <t>09.06.2025 21:00:00</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>31.12.2024 17:00:00</t>
+          <t>31.12.2025 17:00:00</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>16.08.2022 15:00:00</t>
+          <t>16.08.2025 15:00:00</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>16.08.2022 14:00:00</t>
+          <t>16.08.2025 14:00:00</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>24.11.2022 8:00:00</t>
+          <t>24.11.2025 8:00:00</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>19.03.2024 7:00:00</t>
+          <t>19.03.2025 7:00:00</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>19.03.2024 10:00:00</t>
+          <t>19.03.2025 10:00:00</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>10.04.2022 16:00:00</t>
+          <t>10.04.2025 16:00:00</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>01.04.2020 18:00:00</t>
+          <t>01.04.2025 18:00:00</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>20.06.2022 7:00:00</t>
+          <t>20.06.2025 7:00:00</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>21.06.2022 10:00:00</t>
+          <t>21.06.2025 10:00:00</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>06.01.2020 17:00:00</t>
+          <t>06.01.2025 17:00:00</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>08.12.2023 8:00:00</t>
+          <t>08.12.2025 8:00:00</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>18.04.2021 17:00:00</t>
+          <t>18.04.2025 17:00:00</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>18.04.2021 13:00:00</t>
+          <t>18.04.2025 13:00:00</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>27.03.2021 14:00:00</t>
+          <t>27.03.2025 14:00:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>25.01.2021 16:00:00</t>
+          <t>25.01.2025 16:00:00</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>26.01.2021 7:00:00</t>
+          <t>26.01.2025 7:00:00</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>21.02.2021 9:00:00</t>
+          <t>21.02.2025 9:00:00</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>21.01.2022 12:00:00</t>
+          <t>21.01.2025 12:00:00</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>14.10.2022 9:00:00</t>
+          <t>14.10.2025 9:00:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>12.12.2023 10:00:00</t>
+          <t>12.12.2025 10:00:00</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>12.12.2023 14:00:00</t>
+          <t>12.12.2025 14:00:00</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>02.07.2021 11:00:00</t>
+          <t>02.07.2025 11:00:00</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>12.05.2024 8:00:00</t>
+          <t>12.05.2025 8:00:00</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>12.05.2024 18:00:00</t>
+          <t>12.05.2025 18:00:00</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>06.05.2020 18:00:00</t>
+          <t>06.05.2025 18:00:00</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>16.08.2021 7:00:00</t>
+          <t>16.08.2025 7:00:00</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>17.08.2021 20:00:00</t>
+          <t>17.08.2025 20:00:00</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>26.08.2020 12:00:00</t>
+          <t>26.08.2025 12:00:00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>11.05.2023 10:00:00</t>
+          <t>11.05.2025 10:00:00</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>15.02.2022 14:00:00</t>
+          <t>15.02.2025 14:00:00</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>17.02.2022 19:00:00</t>
+          <t>17.02.2025 19:00:00</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>14.08.2022 11:00:00</t>
+          <t>14.08.2025 11:00:00</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>13.03.2021 13:00:00</t>
+          <t>13.03.2025 13:00:00</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>13.03.2021 10:00:00</t>
+          <t>13.03.2025 10:00:00</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>28.05.2020 18:00:00</t>
+          <t>28.05.2025 18:00:00</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>13.03.2023 12:00:00</t>
+          <t>13.03.2025 12:00:00</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>13.03.2023 8:00:00</t>
+          <t>13.03.2025 8:00:00</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>20.12.2022 16:00:00</t>
+          <t>20.12.2025 16:00:00</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
